--- a/frontend/kskcolle/public/data/erelijsten/Megalijst.xlsx
+++ b/frontend/kskcolle/public/data/erelijsten/Megalijst.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a822bf281130dcc6/Documenten/Schaken/Website KSK Colle/_/erelijsten/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a822bf281130dcc6/Documenten/Schaken/KSKColle/frontend/kskcolle/public/data/erelijsten/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{254F70F8-4CCB-41FD-AA27-B62CEEBACA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2739D71A-2955-43D7-9D9F-DD7FBF2A3D6E}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{254F70F8-4CCB-41FD-AA27-B62CEEBACA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FCF74B76-2EF4-422A-B9AE-5C9BF7C81D1C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Megaschaak" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
   <si>
     <t>Jaar</t>
   </si>
@@ -944,12 +944,27 @@
       </c>
     </row>
     <row r="18" spans="1:7" ht="15.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="10"/>
+      <c r="A18" s="4">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="7">
+        <v>2</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="8">
+        <v>3</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="19" spans="1:7" ht="15.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
